--- a/Saves/130/Расписание_гр130_Заяц_Иван_Спанович_утро_четная_Песина.xlsx
+++ b/Saves/130/Расписание_гр130_Заяц_Иван_Спанович_утро_четная_Песина.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1938,11 +1938,11 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Тема №5 - Пешеходные переходы и остановочные пункты маршрутных транспортных средств. Преимущество маршрутных транспортных средств.</t>
+          <t>Тема №5 - Пешеходные переходы и остановочные пункты маршрутных транспортных средств. Преимущество маршрутных транспортных средств.; Тема №8 - ПДД - Итоговое занятие. ПЗ.</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2209,20 +2209,20 @@
     <row r="71" ht="35" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>ПДД</t>
+          <t>Экзамен</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Тема №8 - ПДД - Итоговое занятие. ПЗ.</t>
+          <t>Тема №1 - Теоретический экзамен</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -2231,62 +2231,6 @@
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Песина</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="35" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>28.08.2026</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Экзамен</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>Заяц Иван Спанович</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Песина</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="35" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>02.09.2026</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>Экзамен</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Тема №1 - Теоретический экзамен</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Заяц Иван Спанович</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>Песина</t>
         </is>
